--- a/upload/pytest-temp/test_comparison_excel_matches_0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_matches_0/comparison.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Сравнение систем'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Сравнение систем'!$A$1:$C$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Сравнение систем'!$A$1:$C$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,12 +466,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.052631578947368</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.368421052631579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.7518796992481203</v>
+        <v>0</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.9774436090225563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -564,11 +564,15 @@
           <t>Стоимость ЛКМ, руб/м²</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>141.16</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -577,11 +581,15 @@
           <t>Стоимость ЛКМ на объект, руб</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>14115.79</v>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -590,11 +598,15 @@
           <t>Разбавитель, руб/м²</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -603,11 +615,15 @@
           <t>ЛКМ + разбавитель, руб/м²</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>141.16</v>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -616,11 +632,15 @@
           <t>Стоимость объекта, руб</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>14115.79</v>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -631,12 +651,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>эпоксид</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>эпоксид</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -702,473 +722,6 @@
       </c>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: материал</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 1</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: DFT, мкм</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: WFT, мкм</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>157.1428571428571</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>157.1428571428571</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: расход, кг/м²</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>0.231578947368421</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>0.231578947368421</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: расход, л/м²</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>0.1654135338345865</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>0.1654135338345865</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: стоимость, руб/м²</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>23.39</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Слой 1: разбавитель, л/м²</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: материал</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 2</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: DFT, мкм</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: WFT, мкм</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>171.4285714285714</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>171.4285714285714</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: расход, кг/м²</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>0.2526315789473684</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0.2526315789473684</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: расход, л/м²</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>0.1804511278195489</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>0.1804511278195489</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: стоимость, руб/м²</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>25.77</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Слой 2: разбавитель, л/м²</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: материал</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 3</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: DFT, мкм</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: WFT, мкм</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>185.7142857142857</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>185.7142857142857</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: расход, кг/м²</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>0.2736842105263158</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>0.2736842105263158</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: расход, л/м²</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>0.1954887218045113</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0.1954887218045113</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: стоимость, руб/м²</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>28.19</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>28.19</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Слой 3: разбавитель, л/м²</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: материал</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 4</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: DFT, мкм</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: WFT, мкм</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: расход, кг/м²</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>0.2947368421052631</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>0.2947368421052631</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: расход, л/м²</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: стоимость, руб/м²</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>30.65</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>30.65</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Слой 4: разбавитель, л/м²</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: материал</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Blank Слой 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: DFT, мкм</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: WFT, мкм</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n">
-        <v>214.2857142857143</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: расход, кг/м²</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: расход, л/м²</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n">
-        <v>0.2255639097744361</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: стоимость, руб/м²</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>33.16</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Слой 5: разбавитель, л/м²</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/upload/pytest-temp/test_comparison_excel_matches_0/comparison.xlsx
+++ b/upload/pytest-temp/test_comparison_excel_matches_0/comparison.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Сравнение систем'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Сравнение систем'!$A$1:$C$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Сравнение систем'!$A$1:$C$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,12 +466,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>1.368421052631579</v>
       </c>
     </row>
     <row r="8">
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>0.9774436090225563</v>
       </c>
     </row>
     <row r="9">
@@ -564,15 +564,11 @@
           <t>Стоимость ЛКМ, руб/м²</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B9" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>141.16</v>
       </c>
     </row>
     <row r="10">
@@ -581,15 +577,11 @@
           <t>Стоимость ЛКМ на объект, руб</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B10" s="4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>14115.79</v>
       </c>
     </row>
     <row r="11">
@@ -598,15 +590,11 @@
           <t>Разбавитель, руб/м²</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -615,15 +603,11 @@
           <t>ЛКМ + разбавитель, руб/м²</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B12" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>141.16</v>
       </c>
     </row>
     <row r="13">
@@ -632,15 +616,11 @@
           <t>Стоимость объекта, руб</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B13" s="4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>14115.79</v>
       </c>
     </row>
     <row r="14">
@@ -651,12 +631,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>эпоксид</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>эпоксид</t>
         </is>
       </c>
     </row>
@@ -722,6 +702,473 @@
       </c>
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: материал</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: DFT, мкм</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: WFT, мкм</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>157.1428571428571</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>157.1428571428571</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: расход, кг/м²</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0.231578947368421</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.231578947368421</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: расход, л/м²</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0.1654135338345865</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.1654135338345865</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: стоимость, руб/м²</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>23.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Слой 1: разбавитель, л/м²</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: материал</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 2</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: DFT, мкм</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: WFT, мкм</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>171.4285714285714</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>171.4285714285714</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: расход, кг/м²</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.2526315789473684</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0.2526315789473684</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: расход, л/м²</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0.1804511278195489</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>0.1804511278195489</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: стоимость, руб/м²</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>25.77</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Слой 2: разбавитель, л/м²</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: материал</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 3</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: DFT, мкм</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: WFT, мкм</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>185.7142857142857</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>185.7142857142857</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: расход, кг/м²</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0.2736842105263158</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0.2736842105263158</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: расход, л/м²</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.1954887218045113</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0.1954887218045113</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: стоимость, руб/м²</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>28.19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Слой 3: разбавитель, л/м²</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: материал</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 4</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: DFT, мкм</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: WFT, мкм</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: расход, кг/м²</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0.2947368421052631</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0.2947368421052631</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: расход, л/м²</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: стоимость, руб/м²</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>30.65</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Слой 4: разбавитель, л/м²</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: материал</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Blank Слой 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: DFT, мкм</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: WFT, мкм</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n">
+        <v>214.2857142857143</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: расход, кг/м²</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: расход, л/м²</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n">
+        <v>0.2255639097744361</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: стоимость, руб/м²</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>33.16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Слой 5: разбавитель, л/м²</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
